--- a/test03.07/tables/az_ids.xlsx
+++ b/test03.07/tables/az_ids.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administarator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administarator\Desktop\analytics\test03.07\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13BC115B-17B5-4FB6-B4A1-23318DA9753F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942AEFD7-F286-4227-B959-6924D418A212}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31365" yWindow="3240" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Результат запроса" sheetId="1" r:id="rId1"/>
@@ -25,13 +25,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>ej_id</t>
-  </si>
-  <si>
     <t>course_year</t>
   </si>
   <si>
     <t>liter</t>
+  </si>
+  <si>
+    <t>id</t>
   </si>
 </sst>
 </file>
@@ -396,13 +396,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
